--- a/final_outputs/excel_tables/table_qlp_subsamples_detailed.xlsx
+++ b/final_outputs/excel_tables/table_qlp_subsamples_detailed.xlsx
@@ -4328,13 +4328,13 @@
         <v>0.1</v>
       </c>
       <c r="E122" t="n">
-        <v>1.8e-05</v>
+        <v>-5.7e-05</v>
       </c>
       <c r="F122" t="n">
-        <v>-5.5e-05</v>
+        <v>-0.00095</v>
       </c>
       <c r="G122" t="n">
-        <v>0.000105</v>
+        <v>5.9e-05</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4360,13 +4360,13 @@
         <v>0.1</v>
       </c>
       <c r="E123" t="n">
-        <v>5.9e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="F123" t="n">
-        <v>-3.7e-05</v>
+        <v>-0.000558</v>
       </c>
       <c r="G123" t="n">
-        <v>0.000142</v>
+        <v>0.000133</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4392,13 +4392,13 @@
         <v>0.1</v>
       </c>
       <c r="E124" t="n">
-        <v>-4e-05</v>
+        <v>-0.000295</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.000177</v>
+        <v>-0.000954</v>
       </c>
       <c r="G124" t="n">
-        <v>7.2e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4424,13 +4424,13 @@
         <v>0.1</v>
       </c>
       <c r="E125" t="n">
-        <v>3e-06</v>
+        <v>-0.00032</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.000116</v>
+        <v>-0.001555</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000109</v>
+        <v>3.9e-05</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4456,13 +4456,13 @@
         <v>0.1</v>
       </c>
       <c r="E126" t="n">
-        <v>-3.7e-05</v>
+        <v>0.000177</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.000109</v>
+        <v>-0.000102</v>
       </c>
       <c r="G126" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0.000795</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4488,13 +4488,13 @@
         <v>0.5</v>
       </c>
       <c r="E127" t="n">
-        <v>-3.1e-05</v>
+        <v>-4.1e-05</v>
       </c>
       <c r="F127" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>-7.7e-05</v>
       </c>
       <c r="G127" t="n">
-        <v>1.2e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4523,10 +4523,10 @@
         <v>1e-05</v>
       </c>
       <c r="F128" t="n">
-        <v>-9e-06</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="G128" t="n">
-        <v>4.6e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         <v>0.5</v>
       </c>
       <c r="E129" t="n">
-        <v>1e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="F129" t="n">
-        <v>-3.6e-05</v>
+        <v>-7.9e-05</v>
       </c>
       <c r="G129" t="n">
         <v>3.2e-05</v>
@@ -4584,13 +4584,13 @@
         <v>0.5</v>
       </c>
       <c r="E130" t="n">
-        <v>-1.1e-05</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="F130" t="n">
-        <v>-5.2e-05</v>
+        <v>-0.000136</v>
       </c>
       <c r="G130" t="n">
-        <v>1.7e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4616,13 +4616,13 @@
         <v>0.5</v>
       </c>
       <c r="E131" t="n">
-        <v>-2.8e-05</v>
+        <v>-2.4e-05</v>
       </c>
       <c r="F131" t="n">
-        <v>-6.7e-05</v>
+        <v>-6.2e-05</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>0.9</v>
       </c>
       <c r="E132" t="n">
-        <v>-2.7e-05</v>
+        <v>-0.000163</v>
       </c>
       <c r="F132" t="n">
-        <v>-9.500000000000001e-05</v>
+        <v>-0.000722</v>
       </c>
       <c r="G132" t="n">
-        <v>5.9e-05</v>
+        <v>3.4e-05</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -4680,13 +4680,13 @@
         <v>0.9</v>
       </c>
       <c r="E133" t="n">
-        <v>-2e-05</v>
+        <v>-0.000122</v>
       </c>
       <c r="F133" t="n">
-        <v>-7.6e-05</v>
+        <v>-0.000848</v>
       </c>
       <c r="G133" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4712,13 +4712,13 @@
         <v>0.9</v>
       </c>
       <c r="E134" t="n">
-        <v>-3.4e-05</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.000124</v>
+        <v>-0.00039</v>
       </c>
       <c r="G134" t="n">
-        <v>4.3e-05</v>
+        <v>0.000166</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4744,17 +4744,17 @@
         <v>0.9</v>
       </c>
       <c r="E135" t="n">
-        <v>-6.600000000000001e-05</v>
+        <v>-0.000359</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.000195</v>
+        <v>-0.001306</v>
       </c>
       <c r="G135" t="n">
-        <v>-5e-06</v>
+        <v>3e-05</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4776,13 +4776,13 @@
         <v>0.9</v>
       </c>
       <c r="E136" t="n">
-        <v>-7e-06</v>
+        <v>2.6e-05</v>
       </c>
       <c r="F136" t="n">
-        <v>-9.1e-05</v>
+        <v>-0.000165</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000128</v>
+        <v>0.000598</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4808,13 +4808,13 @@
         <v>0.1</v>
       </c>
       <c r="E137" t="n">
-        <v>-1e-05</v>
+        <v>-0.00038</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.000326</v>
+        <v>-0.001228</v>
       </c>
       <c r="G137" t="n">
-        <v>0.00016</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4840,13 +4840,13 @@
         <v>0.1</v>
       </c>
       <c r="E138" t="n">
-        <v>5.9e-05</v>
+        <v>-0.000221</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.000151</v>
+        <v>-0.001023</v>
       </c>
       <c r="G138" t="n">
-        <v>0.000354</v>
+        <v>0.000362</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4872,13 +4872,13 @@
         <v>0.1</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.3e-05</v>
+        <v>-0.000656</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.000331</v>
+        <v>-0.001343</v>
       </c>
       <c r="G139" t="n">
-        <v>0.000235</v>
+        <v>0.000198</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4904,13 +4904,13 @@
         <v>0.1</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.000186</v>
+        <v>-0.000569</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.000324</v>
+        <v>-0.000942</v>
       </c>
       <c r="G140" t="n">
-        <v>0.000109</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4936,13 +4936,13 @@
         <v>0.1</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.000129</v>
+        <v>0.000267</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.000353</v>
+        <v>-0.00038</v>
       </c>
       <c r="G141" t="n">
-        <v>0.000177</v>
+        <v>0.00069</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4968,13 +4968,13 @@
         <v>0.5</v>
       </c>
       <c r="E142" t="n">
-        <v>-8.4e-05</v>
+        <v>-0.000122</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.000129</v>
+        <v>-0.00022</v>
       </c>
       <c r="G142" t="n">
-        <v>5e-05</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5000,13 +5000,13 @@
         <v>0.5</v>
       </c>
       <c r="E143" t="n">
-        <v>4e-06</v>
+        <v>-2.4e-05</v>
       </c>
       <c r="F143" t="n">
-        <v>-8.8e-05</v>
+        <v>-0.000126</v>
       </c>
       <c r="G143" t="n">
-        <v>5.4e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5032,13 +5032,13 @@
         <v>0.5</v>
       </c>
       <c r="E144" t="n">
-        <v>5e-06</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.000115</v>
+        <v>-0.00025</v>
       </c>
       <c r="G144" t="n">
-        <v>6.1e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5064,13 +5064,13 @@
         <v>0.5</v>
       </c>
       <c r="E145" t="n">
-        <v>-3.7e-05</v>
+        <v>-0.000111</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.000137</v>
+        <v>-0.000306</v>
       </c>
       <c r="G145" t="n">
-        <v>9.2e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5096,17 +5096,17 @@
         <v>0.5</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.000153</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.000201</v>
+        <v>-0.000191</v>
       </c>
       <c r="G146" t="n">
-        <v>-1.3e-05</v>
+        <v>5.5e-05</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5128,13 +5128,13 @@
         <v>0.9</v>
       </c>
       <c r="E147" t="n">
-        <v>1.5e-05</v>
+        <v>-0.000204</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.000151</v>
+        <v>-0.0009990000000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>0.000178</v>
+        <v>0.000109</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5160,13 +5160,13 @@
         <v>0.9</v>
       </c>
       <c r="E148" t="n">
-        <v>-2.6e-05</v>
+        <v>-0.000301</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.000258</v>
+        <v>-0.00103</v>
       </c>
       <c r="G148" t="n">
-        <v>0.000121</v>
+        <v>5.4e-05</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5192,13 +5192,13 @@
         <v>0.9</v>
       </c>
       <c r="E149" t="n">
-        <v>8.6e-05</v>
+        <v>-0.000171</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.000195</v>
+        <v>-0.001081</v>
       </c>
       <c r="G149" t="n">
-        <v>0.00014</v>
+        <v>9.2e-05</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5224,13 +5224,13 @@
         <v>0.9</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.8e-05</v>
+        <v>-0.000359</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.000294</v>
+        <v>-0.001024</v>
       </c>
       <c r="G150" t="n">
-        <v>8.6e-05</v>
+        <v>0.000359</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5256,13 +5256,13 @@
         <v>0.9</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.000111</v>
+        <v>-0.000102</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.000229</v>
+        <v>-0.00042</v>
       </c>
       <c r="G151" t="n">
-        <v>9.2e-05</v>
+        <v>0.000445</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         <v>0.1</v>
       </c>
       <c r="E152" t="n">
-        <v>2e-05</v>
+        <v>-0.000449</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.000447</v>
+        <v>-0.001047</v>
       </c>
       <c r="G152" t="n">
-        <v>0.000252</v>
+        <v>0.000228</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
         <v>0.1</v>
       </c>
       <c r="E153" t="n">
-        <v>-1e-05</v>
+        <v>-0.00032</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.000273</v>
+        <v>-0.000884</v>
       </c>
       <c r="G153" t="n">
-        <v>0.000362</v>
+        <v>0.000271</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.000103</v>
+        <v>-0.0009940000000000001</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.000188</v>
+        <v>-0.0019</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0005240000000000001</v>
+        <v>0.000271</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5384,13 +5384,13 @@
         <v>0.1</v>
       </c>
       <c r="E155" t="n">
-        <v>2e-05</v>
+        <v>-0.000388</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.000265</v>
+        <v>-0.001062</v>
       </c>
       <c r="G155" t="n">
-        <v>0.000334</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5416,13 +5416,13 @@
         <v>0.1</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.000206</v>
+        <v>0.000888</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.000603</v>
+        <v>-0.000476</v>
       </c>
       <c r="G156" t="n">
-        <v>0.000325</v>
+        <v>0.001439</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5448,13 +5448,13 @@
         <v>0.5</v>
       </c>
       <c r="E157" t="n">
-        <v>6e-06</v>
+        <v>-8.1e-05</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.000121</v>
+        <v>-0.000201</v>
       </c>
       <c r="G157" t="n">
-        <v>0.000162</v>
+        <v>0.000117</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5480,13 +5480,13 @@
         <v>0.5</v>
       </c>
       <c r="E158" t="n">
-        <v>1.1e-05</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.00011</v>
+        <v>-0.000173</v>
       </c>
       <c r="G158" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="E159" t="n">
-        <v>-1.8e-05</v>
+        <v>-0.000103</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.000172</v>
+        <v>-0.00042</v>
       </c>
       <c r="G159" t="n">
-        <v>0.000135</v>
+        <v>2.8e-05</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5544,13 +5544,13 @@
         <v>0.5</v>
       </c>
       <c r="E160" t="n">
-        <v>-3.2e-05</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.000139</v>
+        <v>-0.000282</v>
       </c>
       <c r="G160" t="n">
-        <v>0.000112</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5576,13 +5576,13 @@
         <v>0.5</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.000116</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.000213</v>
+        <v>-0.000141</v>
       </c>
       <c r="G161" t="n">
-        <v>4.6e-05</v>
+        <v>0.000196</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         <v>0.9</v>
       </c>
       <c r="E162" t="n">
-        <v>8.7e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="F162" t="n">
-        <v>-2.7e-05</v>
+        <v>-0.000541</v>
       </c>
       <c r="G162" t="n">
-        <v>0.000479</v>
+        <v>0.000313</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0.9</v>
       </c>
       <c r="E163" t="n">
-        <v>-5.1e-05</v>
+        <v>-0.000179</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.000303</v>
+        <v>-0.001023</v>
       </c>
       <c r="G163" t="n">
-        <v>0.000127</v>
+        <v>0.000148</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5672,13 +5672,13 @@
         <v>0.9</v>
       </c>
       <c r="E164" t="n">
-        <v>4.5e-05</v>
+        <v>-0.000353</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.000196</v>
+        <v>-0.001376</v>
       </c>
       <c r="G164" t="n">
-        <v>0.000336</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5704,13 +5704,13 @@
         <v>0.9</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.000117</v>
+        <v>-0.00038</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.000342</v>
+        <v>-0.000785</v>
       </c>
       <c r="G165" t="n">
-        <v>0.000111</v>
+        <v>0.000236</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5736,13 +5736,13 @@
         <v>0.9</v>
       </c>
       <c r="E166" t="n">
-        <v>-6.4e-05</v>
+        <v>0.000374</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.000346</v>
+        <v>-0.000227</v>
       </c>
       <c r="G166" t="n">
-        <v>0.000326</v>
+        <v>0.001046</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5768,13 +5768,13 @@
         <v>0.1</v>
       </c>
       <c r="E167" t="n">
-        <v>0.00017</v>
+        <v>-0.000227</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.00028</v>
+        <v>-0.001303</v>
       </c>
       <c r="G167" t="n">
-        <v>0.00035</v>
+        <v>0.000332</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5800,13 +5800,13 @@
         <v>0.1</v>
       </c>
       <c r="E168" t="n">
-        <v>0.000202</v>
+        <v>5.5e-05</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.000295</v>
+        <v>-0.000643</v>
       </c>
       <c r="G168" t="n">
-        <v>0.000751</v>
+        <v>0.000653</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -5832,13 +5832,13 @@
         <v>0.1</v>
       </c>
       <c r="E169" t="n">
-        <v>0.000185</v>
+        <v>-0.001465</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.000511</v>
+        <v>-0.002457</v>
       </c>
       <c r="G169" t="n">
-        <v>0.000614</v>
+        <v>0.000225</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5864,13 +5864,13 @@
         <v>0.1</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.000103</v>
+        <v>-0.000728</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.000355</v>
+        <v>-0.002079</v>
       </c>
       <c r="G170" t="n">
-        <v>0.000443</v>
+        <v>0.000237</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5896,13 +5896,13 @@
         <v>0.1</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.0002</v>
+        <v>0.000828</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.000626</v>
+        <v>-0.000328</v>
       </c>
       <c r="G171" t="n">
-        <v>0.000653</v>
+        <v>0.001828</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5928,13 +5928,13 @@
         <v>0.5</v>
       </c>
       <c r="E172" t="n">
-        <v>-4.3e-05</v>
+        <v>-0.000144</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.00026</v>
+        <v>-0.000431</v>
       </c>
       <c r="G172" t="n">
-        <v>0.00023</v>
+        <v>0.000137</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>0.5</v>
       </c>
       <c r="E173" t="n">
-        <v>-9.6e-05</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.000222</v>
+        <v>-0.00027</v>
       </c>
       <c r="G173" t="n">
-        <v>5.9e-05</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -5992,13 +5992,13 @@
         <v>0.5</v>
       </c>
       <c r="E174" t="n">
-        <v>-4.9e-05</v>
+        <v>-0.000152</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.000183</v>
+        <v>-0.000589</v>
       </c>
       <c r="G174" t="n">
-        <v>0.00011</v>
+        <v>3.3e-05</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6024,13 +6024,13 @@
         <v>0.5</v>
       </c>
       <c r="E175" t="n">
-        <v>5e-05</v>
+        <v>-0.000248</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.000183</v>
+        <v>-0.000606</v>
       </c>
       <c r="G175" t="n">
-        <v>0.00025</v>
+        <v>0.000201</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6056,13 +6056,13 @@
         <v>0.5</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.000141</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.000312</v>
+        <v>-0.000229</v>
       </c>
       <c r="G176" t="n">
-        <v>6.8e-05</v>
+        <v>0.000392</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         <v>0.9</v>
       </c>
       <c r="E177" t="n">
-        <v>0.000267</v>
+        <v>-0.000276</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.000139</v>
+        <v>-0.0009300000000000001</v>
       </c>
       <c r="G177" t="n">
-        <v>0.000654</v>
+        <v>0.000487</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6120,13 +6120,13 @@
         <v>0.9</v>
       </c>
       <c r="E178" t="n">
-        <v>-4.1e-05</v>
+        <v>-0.000164</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.000467</v>
+        <v>-0.00101</v>
       </c>
       <c r="G178" t="n">
-        <v>0.000205</v>
+        <v>0.000245</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6152,13 +6152,13 @@
         <v>0.9</v>
       </c>
       <c r="E179" t="n">
-        <v>3.1e-05</v>
+        <v>-0.00043</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.000262</v>
+        <v>-0.001315</v>
       </c>
       <c r="G179" t="n">
-        <v>0.000448</v>
+        <v>0.000106</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6184,13 +6184,13 @@
         <v>0.9</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>-0.000821</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.00023</v>
+        <v>-0.0015</v>
       </c>
       <c r="G180" t="n">
-        <v>0.000477</v>
+        <v>0.00026</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6216,13 +6216,13 @@
         <v>0.9</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.000112</v>
+        <v>0.000398</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.000468</v>
+        <v>-0.000224</v>
       </c>
       <c r="G181" t="n">
-        <v>0.00023</v>
+        <v>0.001238</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>

--- a/final_outputs/excel_tables/table_qlp_subsamples_detailed.xlsx
+++ b/final_outputs/excel_tables/table_qlp_subsamples_detailed.xlsx
@@ -4328,13 +4328,13 @@
         <v>0.1</v>
       </c>
       <c r="E122" t="n">
-        <v>-5.7e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.00095</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="G122" t="n">
-        <v>5.9e-05</v>
+        <v>0.000147</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4360,13 +4360,13 @@
         <v>0.1</v>
       </c>
       <c r="E123" t="n">
-        <v>3e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.000558</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="G123" t="n">
-        <v>0.000133</v>
+        <v>0.000167</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4392,13 +4392,13 @@
         <v>0.1</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.000295</v>
+        <v>-0.000125</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.000954</v>
+        <v>-0.000194</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000108</v>
+        <v>3.7e-05</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4424,13 +4424,13 @@
         <v>0.1</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.00032</v>
+        <v>6.4e-05</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.001555</v>
+        <v>-9.3e-05</v>
       </c>
       <c r="G125" t="n">
-        <v>3.9e-05</v>
+        <v>0.000145</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4456,13 +4456,13 @@
         <v>0.1</v>
       </c>
       <c r="E126" t="n">
-        <v>0.000177</v>
+        <v>2.3e-05</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.000102</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="G126" t="n">
-        <v>0.000795</v>
+        <v>0.000148</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4488,13 +4488,13 @@
         <v>0.5</v>
       </c>
       <c r="E127" t="n">
-        <v>-4.1e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="F127" t="n">
-        <v>-7.7e-05</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="G127" t="n">
-        <v>2e-06</v>
+        <v>2.9e-05</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4520,13 +4520,13 @@
         <v>0.5</v>
       </c>
       <c r="E128" t="n">
-        <v>1e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="F128" t="n">
-        <v>-2.2e-05</v>
+        <v>-9e-06</v>
       </c>
       <c r="G128" t="n">
-        <v>4e-05</v>
+        <v>5.4e-05</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4552,13 +4552,13 @@
         <v>0.5</v>
       </c>
       <c r="E129" t="n">
-        <v>-2e-06</v>
+        <v>-8e-06</v>
       </c>
       <c r="F129" t="n">
-        <v>-7.9e-05</v>
+        <v>-3.8e-05</v>
       </c>
       <c r="G129" t="n">
-        <v>3.2e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4584,13 +4584,13 @@
         <v>0.5</v>
       </c>
       <c r="E130" t="n">
-        <v>-5.6e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.000136</v>
+        <v>-6.499999999999999e-05</v>
       </c>
       <c r="G130" t="n">
-        <v>5e-06</v>
+        <v>5e-05</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4616,13 +4616,13 @@
         <v>0.5</v>
       </c>
       <c r="E131" t="n">
-        <v>-2.4e-05</v>
+        <v>-2.3e-05</v>
       </c>
       <c r="F131" t="n">
         <v>-6.2e-05</v>
       </c>
       <c r="G131" t="n">
-        <v>3e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>0.9</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.000163</v>
+        <v>2.3e-05</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.000722</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="G132" t="n">
-        <v>3.4e-05</v>
+        <v>0.000154</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -4680,13 +4680,13 @@
         <v>0.9</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.000122</v>
+        <v>6.9e-05</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.000848</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="G133" t="n">
-        <v>4.7e-05</v>
+        <v>0.000155</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4712,13 +4712,13 @@
         <v>0.9</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.4e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.00039</v>
+        <v>-0.000128</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000166</v>
+        <v>0.0001</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4744,13 +4744,13 @@
         <v>0.9</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.000359</v>
+        <v>-2.6e-05</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.001306</v>
+        <v>-0.000179</v>
       </c>
       <c r="G135" t="n">
-        <v>3e-05</v>
+        <v>0.000166</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         <v>0.9</v>
       </c>
       <c r="E136" t="n">
-        <v>2.6e-05</v>
+        <v>-2.9e-05</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.000165</v>
+        <v>-0.000104</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000598</v>
+        <v>0.000151</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4808,13 +4808,13 @@
         <v>0.1</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.00038</v>
+        <v>-4e-06</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.001228</v>
+        <v>-0.000328</v>
       </c>
       <c r="G137" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>0.000146</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4840,13 +4840,13 @@
         <v>0.1</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.000221</v>
+        <v>7.1e-05</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.001023</v>
+        <v>-0.000261</v>
       </c>
       <c r="G138" t="n">
-        <v>0.000362</v>
+        <v>0.000382</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4872,13 +4872,13 @@
         <v>0.1</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.000656</v>
+        <v>-0.000139</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.001343</v>
+        <v>-0.000328</v>
       </c>
       <c r="G139" t="n">
-        <v>0.000198</v>
+        <v>0.000244</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4904,13 +4904,13 @@
         <v>0.1</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.000569</v>
+        <v>-0.000301</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.000942</v>
+        <v>-0.000583</v>
       </c>
       <c r="G140" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>4.6e-05</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4936,13 +4936,13 @@
         <v>0.1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.000267</v>
+        <v>4.2e-05</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.00038</v>
+        <v>-0.000307</v>
       </c>
       <c r="G141" t="n">
-        <v>0.00069</v>
+        <v>0.000393</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4968,13 +4968,13 @@
         <v>0.5</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.000122</v>
+        <v>-9.399999999999999e-05</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.00022</v>
+        <v>-0.000148</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5000,13 +5000,13 @@
         <v>0.5</v>
       </c>
       <c r="E143" t="n">
-        <v>-2.4e-05</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.000126</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="G143" t="n">
-        <v>5.1e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5032,13 +5032,13 @@
         <v>0.5</v>
       </c>
       <c r="E144" t="n">
-        <v>-5.6e-05</v>
+        <v>-2.3e-05</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.00025</v>
+        <v>-0.000123</v>
       </c>
       <c r="G144" t="n">
-        <v>2.3e-05</v>
+        <v>6.1e-05</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5064,13 +5064,13 @@
         <v>0.5</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.000111</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.000306</v>
+        <v>-0.000205</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0001</v>
+        <v>0.000111</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5096,13 +5096,13 @@
         <v>0.5</v>
       </c>
       <c r="E146" t="n">
-        <v>-9.1e-05</v>
+        <v>-0.000126</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.000191</v>
+        <v>-0.000202</v>
       </c>
       <c r="G146" t="n">
-        <v>5.5e-05</v>
+        <v>1.6e-05</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         <v>0.9</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.000204</v>
+        <v>-5e-06</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.0009990000000000001</v>
+        <v>-0.000199</v>
       </c>
       <c r="G147" t="n">
-        <v>0.000109</v>
+        <v>0.000163</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5160,13 +5160,13 @@
         <v>0.9</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.000301</v>
+        <v>1.6e-05</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.00103</v>
+        <v>-0.000262</v>
       </c>
       <c r="G148" t="n">
-        <v>5.4e-05</v>
+        <v>0.000152</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5192,13 +5192,13 @@
         <v>0.9</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.000171</v>
+        <v>5.2e-05</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.001081</v>
+        <v>-0.000207</v>
       </c>
       <c r="G149" t="n">
-        <v>9.2e-05</v>
+        <v>0.000152</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5224,13 +5224,13 @@
         <v>0.9</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.000359</v>
+        <v>-0.000163</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.001024</v>
+        <v>-0.000323</v>
       </c>
       <c r="G150" t="n">
-        <v>0.000359</v>
+        <v>7.2e-05</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5256,13 +5256,13 @@
         <v>0.9</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.000102</v>
+        <v>-0.000144</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.00042</v>
+        <v>-0.000284</v>
       </c>
       <c r="G151" t="n">
-        <v>0.000445</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         <v>0.1</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.000449</v>
+        <v>6.7e-05</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.001047</v>
+        <v>-0.000622</v>
       </c>
       <c r="G152" t="n">
-        <v>0.000228</v>
+        <v>0.000287</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
         <v>0.1</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.00032</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.000884</v>
+        <v>-0.000343</v>
       </c>
       <c r="G153" t="n">
-        <v>0.000271</v>
+        <v>0.00042</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.1</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.0009940000000000001</v>
+        <v>-0.000287</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.0019</v>
+        <v>-0.000585</v>
       </c>
       <c r="G154" t="n">
-        <v>0.000271</v>
+        <v>0.000407</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5384,13 +5384,13 @@
         <v>0.1</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.000388</v>
+        <v>-0.000189</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.001062</v>
+        <v>-0.000534</v>
       </c>
       <c r="G155" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>0.000324</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5416,13 +5416,13 @@
         <v>0.1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.000888</v>
+        <v>0.000144</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.000476</v>
+        <v>-0.000483</v>
       </c>
       <c r="G156" t="n">
-        <v>0.001439</v>
+        <v>0.00051</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5448,13 +5448,13 @@
         <v>0.5</v>
       </c>
       <c r="E157" t="n">
-        <v>-8.1e-05</v>
+        <v>-1.6e-05</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.000201</v>
+        <v>-0.000128</v>
       </c>
       <c r="G157" t="n">
-        <v>0.000117</v>
+        <v>0.000203</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5480,13 +5480,13 @@
         <v>0.5</v>
       </c>
       <c r="E158" t="n">
-        <v>-5.5e-05</v>
+        <v>-7e-06</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.000173</v>
+        <v>-0.00012</v>
       </c>
       <c r="G158" t="n">
-        <v>4e-05</v>
+        <v>8.1e-05</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.000103</v>
+        <v>-4.5e-05</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.00042</v>
+        <v>-0.000232</v>
       </c>
       <c r="G159" t="n">
-        <v>2.8e-05</v>
+        <v>7.8e-05</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5544,13 +5544,13 @@
         <v>0.5</v>
       </c>
       <c r="E160" t="n">
-        <v>-9.500000000000001e-05</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.000282</v>
+        <v>-0.0002</v>
       </c>
       <c r="G160" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>0.000114</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5576,13 +5576,13 @@
         <v>0.5</v>
       </c>
       <c r="E161" t="n">
-        <v>-3.1e-05</v>
+        <v>-7.1e-05</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.000141</v>
+        <v>-0.000187</v>
       </c>
       <c r="G161" t="n">
-        <v>0.000196</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         <v>0.9</v>
       </c>
       <c r="E162" t="n">
-        <v>8e-06</v>
+        <v>0.000207</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.000541</v>
+        <v>-0.000166</v>
       </c>
       <c r="G162" t="n">
-        <v>0.000313</v>
+        <v>0.000457</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0.9</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.000179</v>
+        <v>4.2e-05</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.001023</v>
+        <v>-0.000283</v>
       </c>
       <c r="G163" t="n">
-        <v>0.000148</v>
+        <v>0.000236</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5672,13 +5672,13 @@
         <v>0.9</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.000353</v>
+        <v>3.5e-05</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.001376</v>
+        <v>-0.00038</v>
       </c>
       <c r="G164" t="n">
-        <v>9.1e-05</v>
+        <v>0.000251</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5704,13 +5704,13 @@
         <v>0.9</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.00038</v>
+        <v>-0.000217</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.000785</v>
+        <v>-0.00051</v>
       </c>
       <c r="G165" t="n">
-        <v>0.000236</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5736,13 +5736,13 @@
         <v>0.9</v>
       </c>
       <c r="E166" t="n">
-        <v>0.000374</v>
+        <v>-3.8e-05</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.000227</v>
+        <v>-0.000243</v>
       </c>
       <c r="G166" t="n">
-        <v>0.001046</v>
+        <v>0.000319</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5768,13 +5768,13 @@
         <v>0.1</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.000227</v>
+        <v>-4e-06</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.001303</v>
+        <v>-0.000448</v>
       </c>
       <c r="G167" t="n">
-        <v>0.000332</v>
+        <v>0.000392</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5800,13 +5800,13 @@
         <v>0.1</v>
       </c>
       <c r="E168" t="n">
-        <v>5.5e-05</v>
+        <v>0.000417</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.000643</v>
+        <v>-0.000245</v>
       </c>
       <c r="G168" t="n">
-        <v>0.000653</v>
+        <v>0.001012</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -5832,13 +5832,13 @@
         <v>0.1</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.001465</v>
+        <v>-7e-06</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.002457</v>
+        <v>-0.000902</v>
       </c>
       <c r="G169" t="n">
-        <v>0.000225</v>
+        <v>0.000612</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5864,13 +5864,13 @@
         <v>0.1</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.000728</v>
+        <v>-0.000225</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.002079</v>
+        <v>-0.001063</v>
       </c>
       <c r="G170" t="n">
-        <v>0.000237</v>
+        <v>0.000476</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5896,13 +5896,13 @@
         <v>0.1</v>
       </c>
       <c r="E171" t="n">
-        <v>0.000828</v>
+        <v>0.000448</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.000328</v>
+        <v>-0.000518</v>
       </c>
       <c r="G171" t="n">
-        <v>0.001828</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5928,13 +5928,13 @@
         <v>0.5</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.000144</v>
+        <v>-7.1e-05</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.000431</v>
+        <v>-0.000391</v>
       </c>
       <c r="G172" t="n">
-        <v>0.000137</v>
+        <v>0.000171</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>0.5</v>
       </c>
       <c r="E173" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-7.3e-05</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.00027</v>
+        <v>-0.000228</v>
       </c>
       <c r="G173" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>0.000104</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -5992,13 +5992,13 @@
         <v>0.5</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.000152</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.000589</v>
+        <v>-0.000226</v>
       </c>
       <c r="G174" t="n">
-        <v>3.3e-05</v>
+        <v>8.4e-05</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6024,13 +6024,13 @@
         <v>0.5</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.000248</v>
+        <v>-3.9e-05</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.000606</v>
+        <v>-0.000206</v>
       </c>
       <c r="G175" t="n">
-        <v>0.000201</v>
+        <v>0.000234</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6056,13 +6056,13 @@
         <v>0.5</v>
       </c>
       <c r="E176" t="n">
-        <v>-3.1e-05</v>
+        <v>-0.00012</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.000229</v>
+        <v>-0.000276</v>
       </c>
       <c r="G176" t="n">
-        <v>0.000392</v>
+        <v>7.9e-05</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         <v>0.9</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.000276</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.0009300000000000001</v>
+        <v>-0.000329</v>
       </c>
       <c r="G177" t="n">
-        <v>0.000487</v>
+        <v>0.000664</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6120,13 +6120,13 @@
         <v>0.9</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.000164</v>
+        <v>-8.7e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.00101</v>
+        <v>-0.000501</v>
       </c>
       <c r="G178" t="n">
-        <v>0.000245</v>
+        <v>0.000398</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6152,13 +6152,13 @@
         <v>0.9</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.00043</v>
+        <v>-0.000229</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.001315</v>
+        <v>-0.001044</v>
       </c>
       <c r="G179" t="n">
-        <v>0.000106</v>
+        <v>0.000342</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6184,13 +6184,13 @@
         <v>0.9</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.000821</v>
+        <v>-6.1e-05</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.0015</v>
+        <v>-0.000319</v>
       </c>
       <c r="G180" t="n">
-        <v>0.00026</v>
+        <v>0.000701</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6216,13 +6216,13 @@
         <v>0.9</v>
       </c>
       <c r="E181" t="n">
-        <v>0.000398</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.000224</v>
+        <v>-0.000376</v>
       </c>
       <c r="G181" t="n">
-        <v>0.001238</v>
+        <v>0.000909</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
